--- a/Yield/RES field datasheet.xlsx
+++ b/Yield/RES field datasheet.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11018"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/zhangdakui/Documents/GitHub/ERW/Yield/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53465CD0-AFDA-6042-9450-54963D923D5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E5E7AEE-7400-484F-BACE-A90A57BFB37C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="18880" xr2:uid="{7065DB47-097C-C04F-ADEF-4C289C6D55B0}"/>
+    <workbookView xWindow="-20" yWindow="760" windowWidth="30240" windowHeight="18880" xr2:uid="{7065DB47-097C-C04F-ADEF-4C289C6D55B0}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -512,6 +512,9 @@
       <c r="B2">
         <v>592</v>
       </c>
+      <c r="C2">
+        <v>122</v>
+      </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
@@ -520,6 +523,9 @@
       <c r="B3">
         <v>526</v>
       </c>
+      <c r="C3">
+        <v>122</v>
+      </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
@@ -528,6 +534,9 @@
       <c r="B4">
         <v>552</v>
       </c>
+      <c r="C4">
+        <v>120</v>
+      </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
@@ -560,6 +569,9 @@
       <c r="B8">
         <v>572</v>
       </c>
+      <c r="C8">
+        <v>166</v>
+      </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
@@ -568,6 +580,9 @@
       <c r="B9">
         <v>580</v>
       </c>
+      <c r="C9">
+        <v>216</v>
+      </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
@@ -575,6 +590,9 @@
       </c>
       <c r="B10">
         <v>520</v>
+      </c>
+      <c r="C10">
+        <v>164</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.2">

--- a/Yield/RES field datasheet.xlsx
+++ b/Yield/RES field datasheet.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/zhangdakui/Documents/GitHub/ERW/Yield/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E5E7AEE-7400-484F-BACE-A90A57BFB37C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB4D7974-B197-FE4F-BE42-9830F1437389}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20" yWindow="760" windowWidth="30240" windowHeight="18880" xr2:uid="{7065DB47-097C-C04F-ADEF-4C289C6D55B0}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="18880" xr2:uid="{7065DB47-097C-C04F-ADEF-4C289C6D55B0}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -545,6 +545,9 @@
       <c r="B5">
         <v>544</v>
       </c>
+      <c r="C5">
+        <v>116</v>
+      </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
@@ -553,6 +556,9 @@
       <c r="B6">
         <v>608</v>
       </c>
+      <c r="C6">
+        <v>120</v>
+      </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
@@ -560,6 +566,9 @@
       </c>
       <c r="B7">
         <v>548</v>
+      </c>
+      <c r="C7">
+        <v>126</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.2">

--- a/Yield/RES field datasheet.xlsx
+++ b/Yield/RES field datasheet.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11018"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/zhangdakui/Documents/GitHub/ERW/Yield/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB4D7974-B197-FE4F-BE42-9830F1437389}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB96D3AC-257A-984E-B1A4-C4B4775137FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="18880" xr2:uid="{7065DB47-097C-C04F-ADEF-4C289C6D55B0}"/>
   </bookViews>
@@ -644,6 +644,9 @@
       <c r="B14">
         <v>632</v>
       </c>
+      <c r="C14">
+        <v>164</v>
+      </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
@@ -652,6 +655,9 @@
       <c r="B15">
         <v>480</v>
       </c>
+      <c r="C15">
+        <v>78</v>
+      </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
@@ -659,6 +665,9 @@
       </c>
       <c r="B16">
         <v>540</v>
+      </c>
+      <c r="C16">
+        <v>120</v>
       </c>
     </row>
   </sheetData>
